--- a/feedback.xlsx
+++ b/feedback.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\dev\react\jam-native\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6DD637B-DF8A-414D-BC72-6E8315E98D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F9C7EE-6051-40CC-BA68-8AF97BB1DA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{BC111119-0A40-40C0-84CD-6F2E98C14B3B}"/>
   </bookViews>
@@ -33,11 +33,26 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>API Enpoints Feedback</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,8 +79,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -382,7 +398,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB5A567-F779-4078-9175-BEDC6203C137}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/feedback.xlsx
+++ b/feedback.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\dev\react\jam-native\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F9C7EE-6051-40CC-BA68-8AF97BB1DA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE969BA-40BD-49B5-8E99-6E3E0CC412F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" xr2:uid="{BC111119-0A40-40C0-84CD-6F2E98C14B3B}"/>
   </bookViews>
@@ -34,9 +34,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>API Enpoints Feedback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- </t>
   </si>
 </sst>
 </file>
@@ -396,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EB5A567-F779-4078-9175-BEDC6203C137}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:1" ht="18.5" x14ac:dyDescent="0.9">
@@ -404,6 +407,11 @@
         <v>0</v>
       </c>
     </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
